--- a/tests/fixtures/synthetic/messy_headers/claim_valuations.xlsx
+++ b/tests/fixtures/synthetic/messy_headers/claim_valuations.xlsx
@@ -11340,10 +11340,10 @@
         <v>45077</v>
       </c>
       <c r="J266">
+        <v>0.09</v>
+      </c>
+      <c r="K266">
         <v>0.03</v>
-      </c>
-      <c r="K266">
-        <v>0.01</v>
       </c>
     </row>
     <row r="267">
@@ -12200,7 +12200,7 @@
         <v>0</v>
       </c>
       <c r="E287">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F287">
         <v>0</v>
@@ -12217,10 +12217,10 @@
         <v>45107</v>
       </c>
       <c r="J287">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="K287">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="288">
@@ -13159,10 +13159,10 @@
         <v>0</v>
       </c>
       <c r="E310">
+        <v>0.13</v>
+      </c>
+      <c r="F310">
         <v>0.04</v>
-      </c>
-      <c r="F310">
-        <v>0.01</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
